--- a/diseases/d106/2000-2004.xlsx
+++ b/diseases/d106/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>79</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.526215700837767</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>128</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>2.850229142835893</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>47</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.9080017460680385</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>78</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>1.736858383915622</v>
       </c>
@@ -2793,9 +2781,6 @@
       <c r="O13" t="n">
         <v>40</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.7727674434621603</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>73</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>1.625521308023595</v>
       </c>
@@ -3733,9 +3715,6 @@
       <c r="O18" t="n">
         <v>46</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.8886825599814845</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>97</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>2.159939272305325</v>
       </c>
@@ -4673,9 +4649,6 @@
       <c r="O23" t="n">
         <v>60</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.159151165193241</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>54</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>1.202440419633892</v>
       </c>
@@ -5613,9 +5583,6 @@
       <c r="O28" t="n">
         <v>55</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.062555234760471</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>84</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>1.870462874986055</v>
       </c>
@@ -6553,9 +6517,6 @@
       <c r="O33" t="n">
         <v>29</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.5602563965100663</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>48</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>1.06883592856346</v>
       </c>
@@ -7493,9 +7451,6 @@
       <c r="O38" t="n">
         <v>24</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.4636604660772963</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>31</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.6902898705305679</v>
       </c>
@@ -8433,9 +8385,6 @@
       <c r="O43" t="n">
         <v>46</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.8886825599814845</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>73</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>1.625521308023595</v>
       </c>
@@ -9373,9 +9319,6 @@
       <c r="O48" t="n">
         <v>62</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.197789537366349</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>55</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>1.224707834812298</v>
       </c>
@@ -10313,9 +10253,6 @@
       <c r="O53" t="n">
         <v>54</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.043236048673917</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>53</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.180173004455487</v>
       </c>
@@ -11253,9 +11187,6 @@
       <c r="O58" t="n">
         <v>65</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>1.255747095626011</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>91</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>2.026334781234893</v>
       </c>
@@ -12193,9 +12121,6 @@
       <c r="O63" t="n">
         <v>56</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.079420066149175</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>92</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>2.038258556199552</v>
       </c>
@@ -13133,9 +13055,6 @@
       <c r="O68" t="n">
         <v>69</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.329999724362376</v>
       </c>
@@ -13529,9 +13448,6 @@
       <c r="O70" t="n">
         <v>97</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>2.149033477732136</v>
       </c>
@@ -14073,9 +13989,6 @@
       <c r="O73" t="n">
         <v>65</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>1.252898291066006</v>
       </c>
@@ -14469,9 +14382,6 @@
       <c r="O75" t="n">
         <v>73</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.617313854375731</v>
       </c>
@@ -15013,9 +14923,6 @@
       <c r="O78" t="n">
         <v>64</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>1.233622932741914</v>
       </c>
@@ -15409,9 +15316,6 @@
       <c r="O80" t="n">
         <v>87</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>1.927483634666967</v>
       </c>
@@ -15953,9 +15857,6 @@
       <c r="O83" t="n">
         <v>60</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>1.156521499445544</v>
       </c>
@@ -16349,9 +16250,6 @@
       <c r="O85" t="n">
         <v>66</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>1.462228964230113</v>
       </c>
@@ -16893,9 +16791,6 @@
       <c r="O88" t="n">
         <v>61</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>1.175796857769637</v>
       </c>
@@ -17289,9 +17184,6 @@
       <c r="O90" t="n">
         <v>54</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.196369152551911</v>
       </c>
@@ -17833,9 +17725,6 @@
       <c r="O93" t="n">
         <v>29</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.5589853913986798</v>
       </c>
@@ -18229,9 +18118,6 @@
       <c r="O95" t="n">
         <v>57</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>1.262834105471461</v>
       </c>
@@ -18773,9 +18659,6 @@
       <c r="O98" t="n">
         <v>16</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.3084057331854785</v>
       </c>
@@ -19169,9 +19052,6 @@
       <c r="O100" t="n">
         <v>33</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.7311144821150566</v>
       </c>
@@ -19713,9 +19593,6 @@
       <c r="O103" t="n">
         <v>55</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>1.060144707825082</v>
       </c>
@@ -20109,9 +19986,6 @@
       <c r="O105" t="n">
         <v>49</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.085594231019327</v>
       </c>
@@ -20653,9 +20527,6 @@
       <c r="O108" t="n">
         <v>61</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.175796857769637</v>
       </c>
@@ -21049,9 +20920,6 @@
       <c r="O110" t="n">
         <v>82</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>1.816708713134383</v>
       </c>
@@ -21593,9 +21461,6 @@
       <c r="O113" t="n">
         <v>62</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>1.195072216093729</v>
       </c>
@@ -21989,9 +21854,6 @@
       <c r="O115" t="n">
         <v>84</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>1.861018681747417</v>
       </c>
@@ -22533,9 +22395,6 @@
       <c r="O118" t="n">
         <v>68</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>1.310724366038283</v>
       </c>
@@ -22929,9 +22788,6 @@
       <c r="O120" t="n">
         <v>95</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>2.104723509119102</v>
       </c>
@@ -23473,9 +23329,6 @@
       <c r="O123" t="n">
         <v>67</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.288326264203797</v>
       </c>
@@ -23869,9 +23722,6 @@
       <c r="O125" t="n">
         <v>79</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>1.740849631578924</v>
       </c>
@@ -24413,9 +24263,6 @@
       <c r="O128" t="n">
         <v>61</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.172953762931815</v>
       </c>
@@ -24809,9 +24656,6 @@
       <c r="O130" t="n">
         <v>79</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>1.740849631578924</v>
       </c>
@@ -25353,9 +25197,6 @@
       <c r="O133" t="n">
         <v>60</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>1.153725012719818</v>
       </c>
@@ -25749,9 +25590,6 @@
       <c r="O135" t="n">
         <v>76</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>1.674741417721497</v>
       </c>
@@ -26293,9 +26131,6 @@
       <c r="O138" t="n">
         <v>57</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>1.096038762083827</v>
       </c>
@@ -26689,9 +26524,6 @@
       <c r="O140" t="n">
         <v>77</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.696777489007306</v>
       </c>
@@ -27233,9 +27065,6 @@
       <c r="O143" t="n">
         <v>60</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.153725012719818</v>
       </c>
@@ -27629,9 +27458,6 @@
       <c r="O145" t="n">
         <v>73</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>1.608633203864069</v>
       </c>
@@ -28173,9 +27999,6 @@
       <c r="O148" t="n">
         <v>50</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.9614375105998486</v>
       </c>
@@ -28569,9 +28392,6 @@
       <c r="O150" t="n">
         <v>61</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>1.344200348434359</v>
       </c>
@@ -29113,9 +28933,6 @@
       <c r="O153" t="n">
         <v>34</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.6537775072078971</v>
       </c>
@@ -29509,9 +29326,6 @@
       <c r="O155" t="n">
         <v>62</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>1.366236419720168</v>
       </c>
@@ -30053,9 +29867,6 @@
       <c r="O158" t="n">
         <v>15</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -30449,9 +30260,6 @@
       <c r="O160" t="n">
         <v>22</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.4847935682878017</v>
       </c>
@@ -30993,9 +30801,6 @@
       <c r="O163" t="n">
         <v>39</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.7499212582678818</v>
       </c>
@@ -31389,9 +31194,6 @@
       <c r="O165" t="n">
         <v>41</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.9034789227181759</v>
       </c>
@@ -31933,9 +31735,6 @@
       <c r="O168" t="n">
         <v>76</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.46138501611177</v>
       </c>
@@ -32329,9 +32128,6 @@
       <c r="O170" t="n">
         <v>87</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>1.917138201865398</v>
       </c>
@@ -32873,9 +32669,6 @@
       <c r="O173" t="n">
         <v>59</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>1.134496262507821</v>
       </c>
@@ -33269,9 +33062,6 @@
       <c r="O175" t="n">
         <v>95</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>2.093426772151871</v>
       </c>
@@ -33813,9 +33603,6 @@
       <c r="O178" t="n">
         <v>71</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>1.365241265051785</v>
       </c>
@@ -34209,9 +33996,6 @@
       <c r="O180" t="n">
         <v>135</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.974869623584238</v>
       </c>
@@ -34753,9 +34537,6 @@
       <c r="O183" t="n">
         <v>62</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>1.189344623155197</v>
       </c>
@@ -35149,9 +34930,6 @@
       <c r="O185" t="n">
         <v>130</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>2.84796115556243</v>
       </c>
@@ -35693,9 +35471,6 @@
       <c r="O188" t="n">
         <v>63</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>1.208527600948023</v>
       </c>
@@ -36089,9 +35864,6 @@
       <c r="O190" t="n">
         <v>94</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>2.05929498940668</v>
       </c>
@@ -36633,9 +36405,6 @@
       <c r="O193" t="n">
         <v>48</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.9207829340556364</v>
       </c>
@@ -37029,9 +36798,6 @@
       <c r="O195" t="n">
         <v>70</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>1.533517545302847</v>
       </c>
@@ -37573,9 +37339,6 @@
       <c r="O198" t="n">
         <v>85</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>1.63055311239019</v>
       </c>
@@ -37969,9 +37732,6 @@
       <c r="O200" t="n">
         <v>103</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>2.256461530945618</v>
       </c>
@@ -38513,9 +38273,6 @@
       <c r="O203" t="n">
         <v>83</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>1.592187156804538</v>
       </c>
@@ -38909,9 +38666,6 @@
       <c r="O205" t="n">
         <v>74</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>1.621147119320152</v>
       </c>
@@ -39453,9 +39207,6 @@
       <c r="O208" t="n">
         <v>62</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>1.189344623155197</v>
       </c>
@@ -39849,9 +39600,6 @@
       <c r="O210" t="n">
         <v>68</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>1.489702758294194</v>
       </c>
@@ -40393,9 +40141,6 @@
       <c r="O213" t="n">
         <v>38</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.7289531561273788</v>
       </c>
@@ -40789,9 +40534,6 @@
       <c r="O215" t="n">
         <v>49</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>1.073462281711993</v>
       </c>
@@ -41333,9 +41075,6 @@
       <c r="O218" t="n">
         <v>25</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.479574444820644</v>
       </c>
@@ -41729,9 +41468,6 @@
       <c r="O220" t="n">
         <v>37</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.8105735596600762</v>
       </c>
@@ -42273,9 +42009,6 @@
       <c r="O223" t="n">
         <v>51</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.9783318674341136</v>
       </c>
@@ -42669,9 +42402,6 @@
       <c r="O225" t="n">
         <v>74</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>1.621147119320152</v>
       </c>
@@ -43213,9 +42943,6 @@
       <c r="O228" t="n">
         <v>39</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.7481361339202046</v>
       </c>
@@ -43609,9 +43336,6 @@
       <c r="O230" t="n">
         <v>89</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>1.949758021885048</v>
       </c>
@@ -44153,9 +43877,6 @@
       <c r="O233" t="n">
         <v>73</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>1.40035737887628</v>
       </c>
@@ -44549,9 +44270,6 @@
       <c r="O235" t="n">
         <v>101</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>2.212646743936965</v>
       </c>
@@ -45093,9 +44811,6 @@
       <c r="O238" t="n">
         <v>148</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>2.839080713338212</v>
       </c>
@@ -45489,9 +45204,6 @@
       <c r="O240" t="n">
         <v>117</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>2.563165040006187</v>
       </c>
@@ -46033,9 +45745,6 @@
       <c r="O243" t="n">
         <v>68</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>1.300651779559416</v>
       </c>
@@ -46429,9 +46138,6 @@
       <c r="O245" t="n">
         <v>131</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>2.852947437710194</v>
       </c>
@@ -46973,9 +46679,6 @@
       <c r="O248" t="n">
         <v>72</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>1.377160707768793</v>
       </c>
@@ -47369,9 +47072,6 @@
       <c r="O250" t="n">
         <v>91</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>1.981818449096394</v>
       </c>
@@ -47913,9 +47613,6 @@
       <c r="O253" t="n">
         <v>72</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>1.377160707768793</v>
       </c>
@@ -48309,9 +48006,6 @@
       <c r="O255" t="n">
         <v>102</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>2.221378920965189</v>
       </c>
@@ -48853,9 +48547,6 @@
       <c r="O258" t="n">
         <v>72</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>1.377160707768793</v>
       </c>
@@ -49249,9 +48940,6 @@
       <c r="O260" t="n">
         <v>100</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>2.177822471534499</v>
       </c>
@@ -49793,9 +49481,6 @@
       <c r="O263" t="n">
         <v>68</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>1.300651779559416</v>
       </c>
@@ -50189,9 +49874,6 @@
       <c r="O265" t="n">
         <v>71</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>1.546253954789494</v>
       </c>
@@ -50733,9 +50415,6 @@
       <c r="O268" t="n">
         <v>63</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>1.205015619297694</v>
       </c>
@@ -51129,9 +50808,6 @@
       <c r="O270" t="n">
         <v>92</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>2.003596673811739</v>
       </c>
@@ -51673,9 +51349,6 @@
       <c r="O273" t="n">
         <v>35</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.6694531218320522</v>
       </c>
@@ -52069,9 +51742,6 @@
       <c r="O275" t="n">
         <v>60</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>1.3066934829207</v>
       </c>
@@ -52613,9 +52283,6 @@
       <c r="O278" t="n">
         <v>38</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.7268348179890852</v>
       </c>
@@ -53009,9 +52676,6 @@
       <c r="O280" t="n">
         <v>44</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.9582418874751797</v>
       </c>
@@ -53553,9 +53217,6 @@
       <c r="O283" t="n">
         <v>59</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>1.128506691088317</v>
       </c>
@@ -53949,9 +53610,6 @@
       <c r="O285" t="n">
         <v>99</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>2.156044246819154</v>
       </c>
@@ -54493,9 +54151,6 @@
       <c r="O288" t="n">
         <v>71</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>1.358033475716449</v>
       </c>
@@ -54889,9 +54544,6 @@
       <c r="O290" t="n">
         <v>102</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>2.221378920965189</v>
       </c>
@@ -55433,9 +55085,6 @@
       <c r="O293" t="n">
         <v>61</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>1.166761155193005</v>
       </c>
@@ -55829,9 +55478,6 @@
       <c r="O295" t="n">
         <v>96</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>2.090709572673119</v>
       </c>
@@ -56373,9 +56019,6 @@
       <c r="O298" t="n">
         <v>58</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>1.109379459035972</v>
       </c>
@@ -56768,9 +56411,6 @@
       </c>
       <c r="O300" t="n">
         <v>136</v>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>2.961838561286919</v>
